--- a/artfynd/A 4568-2026 artfynd.xlsx
+++ b/artfynd/A 4568-2026 artfynd.xlsx
@@ -1631,7 +1631,7 @@
         <v>131187727</v>
       </c>
       <c r="B10" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>131187799</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>131191997</v>
       </c>
       <c r="B12" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>131191949</v>
       </c>
       <c r="B13" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,48 +2070,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131187780</v>
+        <v>131187835</v>
       </c>
       <c r="B14" t="n">
-        <v>79254</v>
+        <v>57086</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svatå, Dlr</t>
+          <t>Svartå, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511335</v>
+        <v>511382</v>
       </c>
       <c r="R14" t="n">
-        <v>6697864</v>
+        <v>6697458</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2148,7 +2153,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Betad tallkrona.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,7 +2162,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2176,53 +2180,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131187835</v>
+        <v>131187780</v>
       </c>
       <c r="B15" t="n">
-        <v>57080</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartå, Dlr</t>
+          <t>Svatå, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511382</v>
+        <v>511335</v>
       </c>
       <c r="R15" t="n">
-        <v>6697458</v>
+        <v>6697864</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2259,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Betad tallkrona.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,6 +2267,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>131192467</v>
       </c>
       <c r="B16" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>131187861</v>
       </c>
       <c r="B17" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>131187741</v>
       </c>
       <c r="B18" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>131187762</v>
       </c>
       <c r="B19" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>131187791</v>
       </c>
       <c r="B20" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>131191884</v>
       </c>
       <c r="B21" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>131191374</v>
       </c>
       <c r="B22" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4568-2026 artfynd.xlsx
+++ b/artfynd/A 4568-2026 artfynd.xlsx
@@ -1959,37 +1959,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131191949</v>
+        <v>131187835</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>57086</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1997,13 +2002,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511393</v>
+        <v>511382</v>
       </c>
       <c r="R13" t="n">
-        <v>6697824</v>
+        <v>6697458</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2030,19 +2035,14 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:33</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Betad tallkrona.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,61 +2051,55 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131187835</v>
+        <v>131191949</v>
       </c>
       <c r="B14" t="n">
-        <v>57086</v>
+        <v>79260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2113,13 +2107,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511382</v>
+        <v>511393</v>
       </c>
       <c r="R14" t="n">
-        <v>6697458</v>
+        <v>6697824</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2146,14 +2140,19 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Betad tallkrona.</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,18 +2161,19 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2617,48 +2617,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131187762</v>
+        <v>131187791</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>57086</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartå, Dlr</t>
+          <t>Svatå, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511511</v>
+        <v>511301</v>
       </c>
       <c r="R19" t="n">
-        <v>6697866</v>
+        <v>6697864</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,18 +2698,12 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På äldre tall.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2723,53 +2722,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131187791</v>
+        <v>131187762</v>
       </c>
       <c r="B20" t="n">
-        <v>57086</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svatå, Dlr</t>
+          <t>Svartå, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511301</v>
+        <v>511511</v>
       </c>
       <c r="R20" t="n">
-        <v>6697864</v>
+        <v>6697866</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2804,12 +2798,18 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På äldre tall.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4568-2026 artfynd.xlsx
+++ b/artfynd/A 4568-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67654838</v>
+        <v>67654781</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511628.8732865983</v>
+        <v>511337</v>
       </c>
       <c r="R2" t="n">
-        <v>6697811.226795617</v>
+        <v>6697766</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,27 +745,18 @@
           <t>2017-09-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-21</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,57 +779,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67648615</v>
+        <v>67648614</v>
       </c>
       <c r="B3" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dragån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511502.9820933746</v>
+        <v>511503</v>
       </c>
       <c r="R3" t="n">
-        <v>6697881.952265475</v>
+        <v>6697882</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,27 +849,18 @@
           <t>2017-09-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-09-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -919,16 +886,11 @@
         <v>67648629</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -958,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511402.2302332874</v>
+        <v>511402</v>
       </c>
       <c r="R4" t="n">
-        <v>6697511.167301412</v>
+        <v>6697511</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,19 +953,9 @@
           <t>2017-09-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,16 +990,11 @@
         <v>67648630</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1077,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511467.1363722338</v>
+        <v>511467</v>
       </c>
       <c r="R5" t="n">
-        <v>6697639.804641249</v>
+        <v>6697640</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1110,19 +1057,9 @@
           <t>2017-09-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-09-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,19 +1091,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67654845</v>
+        <v>67654831</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1196,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511488.0602225353</v>
+        <v>511534</v>
       </c>
       <c r="R6" t="n">
-        <v>6697907.095378227</v>
+        <v>6697783</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,19 +1161,9 @@
           <t>2017-09-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-09-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,19 +1194,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>67654831</v>
+        <v>67654838</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1314,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511533.9713751628</v>
+        <v>511629</v>
       </c>
       <c r="R7" t="n">
-        <v>6697782.769176139</v>
+        <v>6697811</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1347,19 +1264,9 @@
           <t>2017-09-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-09-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,37 +1297,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67648614</v>
+        <v>67654845</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1432,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511502.9820933746</v>
+        <v>511488</v>
       </c>
       <c r="R8" t="n">
-        <v>6697881.952265475</v>
+        <v>6697907</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1465,40 +1367,29 @@
           <t>2017-09-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-09-21</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1509,55 +1400,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67654781</v>
+        <v>131187741</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dragån, Dlr</t>
+          <t>Svartå, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511337.1114939527</v>
+        <v>511476</v>
       </c>
       <c r="R9" t="n">
-        <v>6697765.848579969</v>
+        <v>6697750</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,22 +1468,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt på äldre tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,58 +1494,49 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
-        </is>
-      </c>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131187727</v>
+        <v>131187762</v>
       </c>
       <c r="B10" t="n">
-        <v>57086</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1671,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511543</v>
+        <v>511511</v>
       </c>
       <c r="R10" t="n">
-        <v>6697760</v>
+        <v>6697866</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1709,12 +1582,18 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På äldre tall.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1733,14 +1612,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131187799</v>
+        <v>131187780</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1767,14 +1646,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartå, Dlr</t>
+          <t>Svatå, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511308</v>
+        <v>511335</v>
       </c>
       <c r="R11" t="n">
-        <v>6697583</v>
+        <v>6697864</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1839,42 +1718,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131191997</v>
+        <v>131187799</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1882,13 +1756,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511355</v>
+        <v>511308</v>
       </c>
       <c r="R12" t="n">
-        <v>6697418</v>
+        <v>6697583</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1915,24 +1789,14 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Riinghack äldre på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,60 +1805,56 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187835</v>
+        <v>131191884</v>
       </c>
       <c r="B13" t="n">
-        <v>57086</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2002,13 +1862,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511382</v>
+        <v>511360</v>
       </c>
       <c r="R13" t="n">
-        <v>6697458</v>
+        <v>6697921</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2035,14 +1895,19 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Betad tallkrona.</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,18 +1916,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2072,11 +1938,11 @@
         <v>131191949</v>
       </c>
       <c r="B14" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2180,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131187780</v>
+        <v>131190798</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2191,40 +2057,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svatå, Dlr</t>
+          <t>Svartå, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511335</v>
+        <v>511355</v>
       </c>
       <c r="R15" t="n">
-        <v>6697864</v>
+        <v>6697418</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2251,14 +2122,24 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,57 +2148,60 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131192467</v>
+        <v>131191374</v>
       </c>
       <c r="B16" t="n">
-        <v>57086</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2325,13 +2209,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511370</v>
+        <v>511332</v>
       </c>
       <c r="R16" t="n">
-        <v>6697492</v>
+        <v>6697755</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2360,7 +2244,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2370,12 +2254,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Två tjäderbetade tallar,</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,44 +2286,40 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131187861</v>
+        <v>131187727</v>
       </c>
       <c r="B17" t="n">
-        <v>58057</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2449,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511287</v>
+        <v>511543</v>
       </c>
       <c r="R17" t="n">
-        <v>6697400</v>
+        <v>6697760</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2511,48 +2391,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131187741</v>
+        <v>131187791</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartå, Dlr</t>
+          <t>Svatå, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511476</v>
+        <v>511301</v>
       </c>
       <c r="R18" t="n">
-        <v>6697750</v>
+        <v>6697864</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2587,18 +2472,12 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt på äldre tall.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2617,10 +2496,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131187791</v>
+        <v>131187835</v>
       </c>
       <c r="B19" t="n">
-        <v>57086</v>
+        <v>57141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2650,20 +2529,20 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svatå, Dlr</t>
+          <t>Svartå, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511301</v>
+        <v>511382</v>
       </c>
       <c r="R19" t="n">
-        <v>6697864</v>
+        <v>6697458</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2696,6 +2575,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Betad tallkrona.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2722,37 +2606,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131187762</v>
+        <v>131192467</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>57141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2760,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511511</v>
+        <v>511370</v>
       </c>
       <c r="R20" t="n">
-        <v>6697866</v>
+        <v>6697492</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2793,14 +2678,24 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På äldre tall.</t>
+          <t>Två tjäderbetade tallar,</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2809,29 +2704,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131191884</v>
+        <v>131187861</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2839,26 +2733,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2866,13 +2769,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511360</v>
+        <v>511287</v>
       </c>
       <c r="R21" t="n">
-        <v>6697921</v>
+        <v>6697400</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2899,96 +2802,80 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131191374</v>
+        <v>67648615</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>97977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221944</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartå, Dlr</t>
+          <t>Dragån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511332</v>
+        <v>511503</v>
       </c>
       <c r="R22" t="n">
-        <v>6697755</v>
+        <v>6697882</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3012,27 +2899,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:51</t>
+          <t>2017-09-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>2017-09-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,15 +2919,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Stig-Åke Svenson, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4568-2026 artfynd.xlsx
+++ b/artfynd/A 4568-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67654781</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67648629</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67648630</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67654831</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67654838</t>
         </is>
       </c>
     </row>
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187741</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187799</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1513,6 +1553,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131191949</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,6 +1678,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131190798</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1753,6 +1803,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131191374</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1858,6 +1913,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187727</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187835</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2084,6 +2149,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131192467</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2193,6 +2263,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187861</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2297,6 +2372,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67648614</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2398,6 +2478,11 @@
       <c r="AY17" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67654845</t>
         </is>
       </c>
     </row>
@@ -2506,6 +2591,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187762</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2612,6 +2702,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187780</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2723,6 +2818,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131191884</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2828,6 +2928,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187791</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2932,8 +3037,36 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67648615</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 4568-2026 artfynd.xlsx
+++ b/artfynd/A 4568-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1561,27 +1561,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131190798</v>
+        <v>135649893</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>57977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1592,25 +1592,21 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartå, Dlr</t>
+          <t>Gyllb.vägen S, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511355</v>
+        <v>511312</v>
       </c>
       <c r="R10" t="n">
-        <v>6697418</v>
+        <v>6697576</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1634,27 +1630,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Hack stubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,13 +1676,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131190798</t>
+          <t>https://artportalen.se/Sighting/135649893</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131191374</v>
+        <v>131190798</v>
       </c>
       <c r="B11" t="n">
         <v>57953</v>
@@ -1729,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511332</v>
+        <v>511355</v>
       </c>
       <c r="R11" t="n">
-        <v>6697755</v>
+        <v>6697418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1764,7 +1760,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1774,7 +1770,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1805,38 +1801,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131191374</t>
+          <t>https://artportalen.se/Sighting/131190798</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131187727</v>
+        <v>131191374</v>
       </c>
       <c r="B12" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,7 +1840,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1854,13 +1850,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511543</v>
+        <v>511332</v>
       </c>
       <c r="R12" t="n">
-        <v>6697760</v>
+        <v>6697755</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1887,9 +1883,24 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,73 +1915,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131187727</t>
+          <t>https://artportalen.se/Sighting/131191374</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187835</v>
+        <v>135649877</v>
       </c>
       <c r="B13" t="n">
-        <v>57141</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartå, Dlr</t>
+          <t>Svartå S, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511382</v>
+        <v>511297</v>
       </c>
       <c r="R13" t="n">
-        <v>6697458</v>
+        <v>6697700</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,17 +1997,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Betad tallkrona.</t>
+          <t>Äldre ringhack tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,24 +2032,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131187835</t>
+          <t>https://artportalen.se/Sighting/135649877</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131192467</v>
+        <v>131187727</v>
       </c>
       <c r="B14" t="n">
         <v>57141</v>
@@ -2067,7 +2080,11 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2075,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511370</v>
+        <v>511543</v>
       </c>
       <c r="R14" t="n">
-        <v>6697492</v>
+        <v>6697760</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2108,24 +2125,9 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Två tjäderbetade tallar,</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,61 +2142,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131192467</t>
+          <t>https://artportalen.se/Sighting/131187727</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131187861</v>
+        <v>131187835</v>
       </c>
       <c r="B15" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2204,10 +2202,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511287</v>
+        <v>511382</v>
       </c>
       <c r="R15" t="n">
-        <v>6697400</v>
+        <v>6697458</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2242,6 +2240,11 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Betad tallkrona.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2265,56 +2268,58 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131187861</t>
+          <t>https://artportalen.se/Sighting/131187835</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>67648614</v>
+        <v>131192467</v>
       </c>
       <c r="B16" t="n">
-        <v>93197</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dragån, Dlr</t>
+          <t>Svartå, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511503</v>
+        <v>511370</v>
       </c>
       <c r="R16" t="n">
-        <v>6697882</v>
+        <v>6697492</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2338,12 +2343,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Två tjäderbetade tallar,</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,75 +2372,72 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson, Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
-        </is>
-      </c>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67648614</t>
+          <t>https://artportalen.se/Sighting/131192467</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>67654845</v>
+        <v>135649876</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>57167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dragån, Dlr</t>
+          <t>Gyllb.vägen S, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511488</v>
+        <v>511305</v>
       </c>
       <c r="R17" t="n">
-        <v>6697907</v>
+        <v>6697726</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2447,12 +2464,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,67 +2504,64 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
-        </is>
-      </c>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67654845</t>
+          <t>https://artportalen.se/Sighting/135649876</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131187762</v>
+        <v>135649891</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>57167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartå, Dlr</t>
+          <t>Svartå S, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511511</v>
+        <v>511363</v>
       </c>
       <c r="R18" t="n">
-        <v>6697866</v>
+        <v>6697457</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2556,17 +2585,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På äldre tall.</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,75 +2614,75 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131187762</t>
+          <t>https://artportalen.se/Sighting/135649891</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131187780</v>
+        <v>135649892</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>57167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svatå, Dlr</t>
+          <t>Svartå S, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511335</v>
+        <v>511330</v>
       </c>
       <c r="R19" t="n">
-        <v>6697864</v>
+        <v>6697576</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,17 +2706,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Spillning färsk</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,61 +2735,65 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131187780</t>
+          <t>https://artportalen.se/Sighting/135649892</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131191884</v>
+        <v>135651515</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>57167</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2748,13 +2801,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511360</v>
+        <v>511332</v>
       </c>
       <c r="R20" t="n">
-        <v>6697921</v>
+        <v>6697512</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2778,22 +2831,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2802,34 +2845,33 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131191884</t>
+          <t>https://artportalen.se/Sighting/135651515</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187791</v>
+        <v>135651550</v>
       </c>
       <c r="B21" t="n">
-        <v>57141</v>
+        <v>57167</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2865,14 +2907,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svatå, Dlr</t>
+          <t>Svartå, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511301</v>
+        <v>511270</v>
       </c>
       <c r="R21" t="n">
-        <v>6697864</v>
+        <v>6697597</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2899,12 +2941,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,16 +2972,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131187791</t>
+          <t>https://artportalen.se/Sighting/135651550</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>67648615</v>
+        <v>135651582</v>
       </c>
       <c r="B22" t="n">
-        <v>97977</v>
+        <v>57167</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2947,40 +2989,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221944</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dragån, Dlr</t>
+          <t>Svartå, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511503</v>
+        <v>511265</v>
       </c>
       <c r="R22" t="n">
-        <v>6697882</v>
+        <v>6697321</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3004,12 +3051,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3024,20 +3071,1398 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651582</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131187861</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Svartå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>511287</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6697400</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187861</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135649878</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>511351</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6697498</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>15-tal . Blommande + plantor</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649878</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135649880</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>511358</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6697496</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>20-tal blommor och plantor</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649880</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>67648614</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Dragån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>511503</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6697882</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
           <t>Stig-Åke Svenson</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX26" t="inlineStr">
         <is>
           <t>Stig-Åke Svenson, Lars-Erik Nilsson</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
+      <c r="AY26" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67648614</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>67654845</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Dragån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>511488</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6697907</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67654845</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131187762</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svartå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>511511</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6697866</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På äldre tall.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187762</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131187780</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Svatå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>511335</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6697864</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187780</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131191884</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Svartå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>511360</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6697921</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131191884</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131187791</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Svatå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>511301</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6697864</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187791</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135649874</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>511312</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6697883</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spillning färsk.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649874</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135649875</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>511324</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6697842</v>
+      </c>
+      <c r="S33" t="n">
+        <v>8</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Balningsgrop, fjädrar +spillning, rätt färsk.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649875</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>67648615</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Dragån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>511503</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6697882</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/67648615</t>
         </is>
@@ -3066,6 +4491,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4568-2026 artfynd.xlsx
+++ b/artfynd/A 4568-2026 artfynd.xlsx
@@ -3205,7 +3205,7 @@
         <v>135649878</v>
       </c>
       <c r="B24" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>135649880</v>
       </c>
       <c r="B25" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 4568-2026 artfynd.xlsx
+++ b/artfynd/A 4568-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1561,27 +1561,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131190798</v>
+        <v>135649893</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>57977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1592,25 +1592,21 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartå, Dlr</t>
+          <t>Gyllb.vägen S, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511355</v>
+        <v>511312</v>
       </c>
       <c r="R10" t="n">
-        <v>6697418</v>
+        <v>6697576</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1634,27 +1630,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Hack stubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,13 +1676,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131190798</t>
+          <t>https://artportalen.se/Sighting/135649893</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131191374</v>
+        <v>131190798</v>
       </c>
       <c r="B11" t="n">
         <v>57953</v>
@@ -1729,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511332</v>
+        <v>511355</v>
       </c>
       <c r="R11" t="n">
-        <v>6697755</v>
+        <v>6697418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1764,7 +1760,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1774,7 +1770,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1805,38 +1801,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131191374</t>
+          <t>https://artportalen.se/Sighting/131190798</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131187727</v>
+        <v>131191374</v>
       </c>
       <c r="B12" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,7 +1840,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1854,13 +1850,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511543</v>
+        <v>511332</v>
       </c>
       <c r="R12" t="n">
-        <v>6697760</v>
+        <v>6697755</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1887,9 +1883,24 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,73 +1915,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131187727</t>
+          <t>https://artportalen.se/Sighting/131191374</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187835</v>
+        <v>135649877</v>
       </c>
       <c r="B13" t="n">
-        <v>57141</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartå, Dlr</t>
+          <t>Svartå S, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511382</v>
+        <v>511297</v>
       </c>
       <c r="R13" t="n">
-        <v>6697458</v>
+        <v>6697700</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,17 +1997,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Betad tallkrona.</t>
+          <t>Äldre ringhack tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,24 +2032,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131187835</t>
+          <t>https://artportalen.se/Sighting/135649877</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131192467</v>
+        <v>131187727</v>
       </c>
       <c r="B14" t="n">
         <v>57141</v>
@@ -2067,7 +2080,11 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2075,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511370</v>
+        <v>511543</v>
       </c>
       <c r="R14" t="n">
-        <v>6697492</v>
+        <v>6697760</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2108,24 +2125,9 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Två tjäderbetade tallar,</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,61 +2142,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131192467</t>
+          <t>https://artportalen.se/Sighting/131187727</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131187861</v>
+        <v>131187835</v>
       </c>
       <c r="B15" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2204,10 +2202,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511287</v>
+        <v>511382</v>
       </c>
       <c r="R15" t="n">
-        <v>6697400</v>
+        <v>6697458</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2242,6 +2240,11 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Betad tallkrona.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2265,56 +2268,58 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131187861</t>
+          <t>https://artportalen.se/Sighting/131187835</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>67648614</v>
+        <v>131192467</v>
       </c>
       <c r="B16" t="n">
-        <v>93197</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dragån, Dlr</t>
+          <t>Svartå, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511503</v>
+        <v>511370</v>
       </c>
       <c r="R16" t="n">
-        <v>6697882</v>
+        <v>6697492</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2338,12 +2343,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Två tjäderbetade tallar,</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,75 +2372,72 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson, Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
-        </is>
-      </c>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67648614</t>
+          <t>https://artportalen.se/Sighting/131192467</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>67654845</v>
+        <v>135649876</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>57167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dragån, Dlr</t>
+          <t>Gyllb.vägen S, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511488</v>
+        <v>511305</v>
       </c>
       <c r="R17" t="n">
-        <v>6697907</v>
+        <v>6697726</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2447,12 +2464,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,67 +2504,64 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
-        </is>
-      </c>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67654845</t>
+          <t>https://artportalen.se/Sighting/135649876</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131187762</v>
+        <v>135649891</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>57167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartå, Dlr</t>
+          <t>Svartå S, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511511</v>
+        <v>511363</v>
       </c>
       <c r="R18" t="n">
-        <v>6697866</v>
+        <v>6697457</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2556,17 +2585,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På äldre tall.</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,75 +2614,75 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131187762</t>
+          <t>https://artportalen.se/Sighting/135649891</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131187780</v>
+        <v>135649892</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>57167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svatå, Dlr</t>
+          <t>Svartå S, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511335</v>
+        <v>511330</v>
       </c>
       <c r="R19" t="n">
-        <v>6697864</v>
+        <v>6697576</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,17 +2706,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Spillning färsk</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,61 +2735,65 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131187780</t>
+          <t>https://artportalen.se/Sighting/135649892</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131191884</v>
+        <v>135651515</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>57167</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2748,13 +2801,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511360</v>
+        <v>511332</v>
       </c>
       <c r="R20" t="n">
-        <v>6697921</v>
+        <v>6697512</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2778,22 +2831,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2802,34 +2845,33 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131191884</t>
+          <t>https://artportalen.se/Sighting/135651515</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187791</v>
+        <v>135651550</v>
       </c>
       <c r="B21" t="n">
-        <v>57141</v>
+        <v>57167</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2865,14 +2907,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svatå, Dlr</t>
+          <t>Svartå, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511301</v>
+        <v>511270</v>
       </c>
       <c r="R21" t="n">
-        <v>6697864</v>
+        <v>6697597</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2899,12 +2941,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,16 +2972,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131187791</t>
+          <t>https://artportalen.se/Sighting/135651550</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>67648615</v>
+        <v>135651582</v>
       </c>
       <c r="B22" t="n">
-        <v>97977</v>
+        <v>57167</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2947,40 +2989,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221944</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dragån, Dlr</t>
+          <t>Svartå, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511503</v>
+        <v>511265</v>
       </c>
       <c r="R22" t="n">
-        <v>6697882</v>
+        <v>6697321</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3004,12 +3051,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3024,20 +3071,1398 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651582</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131187861</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Svartå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>511287</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6697400</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187861</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135649878</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>511351</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6697498</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>15-tal . Blommande + plantor</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649878</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135649880</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>511358</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6697496</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>20-tal blommor och plantor</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649880</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>67648614</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Dragån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>511503</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6697882</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
           <t>Stig-Åke Svenson</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX26" t="inlineStr">
         <is>
           <t>Stig-Åke Svenson, Lars-Erik Nilsson</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
+      <c r="AY26" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67648614</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>67654845</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Dragån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>511488</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6697907</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67654845</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131187762</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svartå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>511511</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6697866</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På äldre tall.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187762</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131187780</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Svatå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>511335</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6697864</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187780</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131191884</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Svartå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>511360</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6697921</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131191884</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131187791</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Svatå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>511301</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6697864</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187791</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135649874</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>511312</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6697883</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spillning färsk.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649874</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135649875</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>511324</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6697842</v>
+      </c>
+      <c r="S33" t="n">
+        <v>8</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Balningsgrop, fjädrar +spillning, rätt färsk.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649875</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>67648615</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Dragån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>511503</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6697882</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/67648615</t>
         </is>
@@ -3066,6 +4491,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4568-2026 artfynd.xlsx
+++ b/artfynd/A 4568-2026 artfynd.xlsx
@@ -3205,7 +3205,7 @@
         <v>135649878</v>
       </c>
       <c r="B24" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>135649880</v>
       </c>
       <c r="B25" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 4568-2026 artfynd.xlsx
+++ b/artfynd/A 4568-2026 artfynd.xlsx
@@ -1564,7 +1564,7 @@
         <v>135649893</v>
       </c>
       <c r="B10" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135649877</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>135649876</v>
       </c>
       <c r="B17" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135649891</v>
       </c>
       <c r="B18" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>135649892</v>
       </c>
       <c r="B19" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>135651515</v>
       </c>
       <c r="B20" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>135651550</v>
       </c>
       <c r="B21" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>135651582</v>
       </c>
       <c r="B22" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>135649878</v>
       </c>
       <c r="B24" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>135649880</v>
       </c>
       <c r="B25" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>135649874</v>
       </c>
       <c r="B32" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>135649875</v>
       </c>
       <c r="B33" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 4568-2026 artfynd.xlsx
+++ b/artfynd/A 4568-2026 artfynd.xlsx
@@ -3205,7 +3205,7 @@
         <v>135649878</v>
       </c>
       <c r="B24" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>135649880</v>
       </c>
       <c r="B25" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 4568-2026 artfynd.xlsx
+++ b/artfynd/A 4568-2026 artfynd.xlsx
@@ -3205,7 +3205,7 @@
         <v>135649878</v>
       </c>
       <c r="B24" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>135649880</v>
       </c>
       <c r="B25" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 4568-2026 artfynd.xlsx
+++ b/artfynd/A 4568-2026 artfynd.xlsx
@@ -1564,7 +1564,7 @@
         <v>135649893</v>
       </c>
       <c r="B10" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135649877</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>135649876</v>
       </c>
       <c r="B17" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135649891</v>
       </c>
       <c r="B18" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>135649892</v>
       </c>
       <c r="B19" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>135651515</v>
       </c>
       <c r="B20" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>135651550</v>
       </c>
       <c r="B21" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>135651582</v>
       </c>
       <c r="B22" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>135649878</v>
       </c>
       <c r="B24" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>135649880</v>
       </c>
       <c r="B25" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>135649874</v>
       </c>
       <c r="B32" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>135649875</v>
       </c>
       <c r="B33" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 4568-2026 artfynd.xlsx
+++ b/artfynd/A 4568-2026 artfynd.xlsx
@@ -1564,7 +1564,7 @@
         <v>135649893</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135649877</v>
       </c>
       <c r="B13" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>135649876</v>
       </c>
       <c r="B17" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135649891</v>
       </c>
       <c r="B18" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>135649892</v>
       </c>
       <c r="B19" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>135651515</v>
       </c>
       <c r="B20" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>135651550</v>
       </c>
       <c r="B21" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>135651582</v>
       </c>
       <c r="B22" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>135649878</v>
       </c>
       <c r="B24" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>135649880</v>
       </c>
       <c r="B25" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>135649874</v>
       </c>
       <c r="B32" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>135649875</v>
       </c>
       <c r="B33" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
